--- a/12-10-2026/PAT_Berth_Window.xlsx
+++ b/12-10-2026/PAT_Berth_Window.xlsx
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -669,9 +669,10 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -714,15 +715,20 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>Waiting for Berth (h)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>Hours Alongside</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Marked</t>
         </is>
@@ -752,15 +758,19 @@
         <v>46309.20833333334</v>
       </c>
       <c r="G4" s="28">
+        <f>(E4-D4)*24</f>
+        <v/>
+      </c>
+      <c r="H4" s="28">
         <f>(F4-E4)*24</f>
         <v/>
       </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr"/>
+      <c r="J4" s="23" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -786,15 +796,19 @@
         <v>46310.625</v>
       </c>
       <c r="G5" s="28">
+        <f>(E5-D5)*24</f>
+        <v/>
+      </c>
+      <c r="H5" s="28">
         <f>(F5-E5)*24</f>
         <v/>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr"/>
+      <c r="J5" s="23" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -820,15 +834,19 @@
         <v>46309.66666666666</v>
       </c>
       <c r="G6" s="28">
+        <f>(E6-D6)*24</f>
+        <v/>
+      </c>
+      <c r="H6" s="28">
         <f>(F6-E6)*24</f>
         <v/>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr"/>
+      <c r="J6" s="23" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -854,15 +872,19 @@
         <v>46310.29166666666</v>
       </c>
       <c r="G7" s="28">
+        <f>(E7-D7)*24</f>
+        <v/>
+      </c>
+      <c r="H7" s="28">
         <f>(F7-E7)*24</f>
         <v/>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr"/>
+      <c r="J7" s="23" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -888,15 +910,19 @@
         <v>46309.625</v>
       </c>
       <c r="G8" s="28">
+        <f>(E8-D8)*24</f>
+        <v/>
+      </c>
+      <c r="H8" s="28">
         <f>(F8-E8)*24</f>
         <v/>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr"/>
+      <c r="J8" s="23" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -922,15 +948,19 @@
         <v>46310.20833333334</v>
       </c>
       <c r="G9" s="28">
+        <f>(E9-D9)*24</f>
+        <v/>
+      </c>
+      <c r="H9" s="28">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>4A</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr"/>
+      <c r="J9" s="23" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -956,15 +986,19 @@
         <v>46307.58333333334</v>
       </c>
       <c r="G10" s="28">
+        <f>(E10-D10)*24</f>
+        <v/>
+      </c>
+      <c r="H10" s="28">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr"/>
+      <c r="J10" s="23" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -990,15 +1024,19 @@
         <v>46309.20833333334</v>
       </c>
       <c r="G11" s="28">
+        <f>(E11-D11)*24</f>
+        <v/>
+      </c>
+      <c r="H11" s="28">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I11" s="23" t="inlineStr"/>
+      <c r="J11" s="23" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1024,15 +1062,19 @@
         <v>46309.91666666666</v>
       </c>
       <c r="G12" s="28">
+        <f>(E12-D12)*24</f>
+        <v/>
+      </c>
+      <c r="H12" s="28">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>7B</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr"/>
+      <c r="J12" s="23" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1058,15 +1100,19 @@
         <v>46308.25</v>
       </c>
       <c r="G13" s="28">
+        <f>(E13-D13)*24</f>
+        <v/>
+      </c>
+      <c r="H13" s="28">
         <f>(F13-E13)*24</f>
         <v/>
       </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr"/>
+      <c r="J13" s="23" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1092,15 +1138,19 @@
         <v>46309.25</v>
       </c>
       <c r="G14" s="28">
+        <f>(E14-D14)*24</f>
+        <v/>
+      </c>
+      <c r="H14" s="28">
         <f>(F14-E14)*24</f>
         <v/>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>1C</t>
         </is>
       </c>
-      <c r="I14" s="23" t="inlineStr"/>
+      <c r="J14" s="23" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1126,15 +1176,19 @@
         <v>46310.625</v>
       </c>
       <c r="G15" s="28">
+        <f>(E15-D15)*24</f>
+        <v/>
+      </c>
+      <c r="H15" s="28">
         <f>(F15-E15)*24</f>
         <v/>
       </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I15" s="23" t="inlineStr"/>
+      <c r="J15" s="23" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="39" t="inlineStr">
@@ -1172,7 +1226,8 @@
       </c>
       <c r="G19" s="40" t="n"/>
       <c r="H19" s="40" t="n"/>
-      <c r="I19" s="41" t="n"/>
+      <c r="I19" s="40" t="n"/>
+      <c r="J19" s="41" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -1199,7 +1254,8 @@
       </c>
       <c r="G20" s="40" t="n"/>
       <c r="H20" s="40" t="n"/>
-      <c r="I20" s="41" t="n"/>
+      <c r="I20" s="40" t="n"/>
+      <c r="J20" s="41" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -1226,13 +1282,14 @@
       </c>
       <c r="G21" s="40" t="n"/>
       <c r="H21" s="40" t="n"/>
-      <c r="I21" s="41" t="n"/>
+      <c r="I21" s="40" t="n"/>
+      <c r="J21" s="41" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="F21:J21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/12-10-2026/PAT_Berth_Window.xlsx
+++ b/12-10-2026/PAT_Berth_Window.xlsx
@@ -171,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -223,22 +223,7 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -248,6 +233,9 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -255,6 +243,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,17 +263,8 @@
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -290,9 +275,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -748,20 +730,20 @@
       <c r="C4" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D4" s="44" t="n">
+      <c r="D4" s="39" t="n">
         <v>46307.33333333334</v>
       </c>
-      <c r="E4" s="44" t="n">
+      <c r="E4" s="39" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F4" s="44" t="n">
+      <c r="F4" s="39" t="n">
         <v>46309.20833333334</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="24">
         <f>(E4-D4)*24</f>
         <v/>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="24">
         <f>(F4-E4)*24</f>
         <v/>
       </c>
@@ -786,20 +768,20 @@
       <c r="C5" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D5" s="44" t="n">
+      <c r="D5" s="39" t="n">
         <v>46308.04166666666</v>
       </c>
-      <c r="E5" s="44" t="n">
+      <c r="E5" s="39" t="n">
         <v>46309.20833333334</v>
       </c>
-      <c r="F5" s="44" t="n">
+      <c r="F5" s="39" t="n">
         <v>46310.625</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="24">
         <f>(E5-D5)*24</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="24">
         <f>(F5-E5)*24</f>
         <v/>
       </c>
@@ -824,20 +806,20 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="39" t="n">
         <v>46307.91666666666</v>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="39" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F6" s="44" t="n">
+      <c r="F6" s="39" t="n">
         <v>46309.66666666666</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="24">
         <f>(E6-D6)*24</f>
         <v/>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="24">
         <f>(F6-E6)*24</f>
         <v/>
       </c>
@@ -862,20 +844,20 @@
       <c r="C7" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="39" t="n">
         <v>46309.33333333334</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="39" t="n">
         <v>46309.66666666666</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="39" t="n">
         <v>46310.29166666666</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="24">
         <f>(E7-D7)*24</f>
         <v/>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="24">
         <f>(F7-E7)*24</f>
         <v/>
       </c>
@@ -900,20 +882,20 @@
       <c r="C8" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="39" t="n">
         <v>46307.875</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="39" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="39" t="n">
         <v>46309.625</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="24">
         <f>(E8-D8)*24</f>
         <v/>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="24">
         <f>(F8-E8)*24</f>
         <v/>
       </c>
@@ -938,20 +920,20 @@
       <c r="C9" s="23" t="n">
         <v>449</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="39" t="n">
         <v>46309.125</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="39" t="n">
         <v>46309.58333333334</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="39" t="n">
         <v>46310.20833333334</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="24">
         <f>(E9-D9)*24</f>
         <v/>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="24">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
@@ -976,20 +958,20 @@
       <c r="C10" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D10" s="44" t="n">
+      <c r="D10" s="39" t="n">
         <v>46305.70833333334</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="39" t="n">
         <v>46306.25</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="39" t="n">
         <v>46307.58333333334</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="24">
         <f>(E10-D10)*24</f>
         <v/>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="24">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
@@ -1014,20 +996,20 @@
       <c r="C11" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="39" t="n">
         <v>46307.16666666666</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="39" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="39" t="n">
         <v>46309.20833333334</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="24">
         <f>(E11-D11)*24</f>
         <v/>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="24">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
@@ -1052,20 +1034,20 @@
       <c r="C12" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D12" s="44" t="n">
+      <c r="D12" s="39" t="n">
         <v>46308.29166666666</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="39" t="n">
         <v>46309.20833333334</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="39" t="n">
         <v>46309.91666666666</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="24">
         <f>(E12-D12)*24</f>
         <v/>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="24">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
@@ -1090,20 +1072,20 @@
       <c r="C13" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="39" t="n">
         <v>46307.45833333334</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="39" t="n">
         <v>46307.625</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="39" t="n">
         <v>46308.25</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="24">
         <f>(E13-D13)*24</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="24">
         <f>(F13-E13)*24</f>
         <v/>
       </c>
@@ -1128,20 +1110,20 @@
       <c r="C14" s="23" t="n">
         <v>537</v>
       </c>
-      <c r="D14" s="44" t="n">
+      <c r="D14" s="39" t="n">
         <v>46307.91666666666</v>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="39" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F14" s="44" t="n">
+      <c r="F14" s="39" t="n">
         <v>46309.25</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="24">
         <f>(E14-D14)*24</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="24">
         <f>(F14-E14)*24</f>
         <v/>
       </c>
@@ -1166,20 +1148,20 @@
       <c r="C15" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="39" t="n">
         <v>46308.625</v>
       </c>
-      <c r="E15" s="44" t="n">
+      <c r="E15" s="39" t="n">
         <v>46309.25</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="39" t="n">
         <v>46310.625</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="24">
         <f>(E15-D15)*24</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="24">
         <f>(F15-E15)*24</f>
         <v/>
       </c>
@@ -1191,7 +1173,7 @@
       <c r="J15" s="23" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1224,10 +1206,10 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G19" s="40" t="n"/>
-      <c r="H19" s="40" t="n"/>
-      <c r="I19" s="40" t="n"/>
-      <c r="J19" s="41" t="n"/>
+      <c r="G19" s="35" t="n"/>
+      <c r="H19" s="35" t="n"/>
+      <c r="I19" s="35" t="n"/>
+      <c r="J19" s="36" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -1240,11 +1222,11 @@
           <t>Berth closed</t>
         </is>
       </c>
-      <c r="C20" s="43" t="n"/>
-      <c r="D20" s="45" t="n">
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="40" t="n">
         <v>46299</v>
       </c>
-      <c r="E20" s="45" t="n">
+      <c r="E20" s="40" t="n">
         <v>46319</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
@@ -1252,38 +1234,38 @@
           <t>Close on 4–24 Oct 2026 to renovate electric channel (INCEDA is alongside at 20D; other vessels are booked from 12/16)  —  Unchanged – conflicts with vessel bookings, please confirm</t>
         </is>
       </c>
-      <c r="G20" s="40" t="n"/>
-      <c r="H20" s="40" t="n"/>
-      <c r="I20" s="40" t="n"/>
-      <c r="J20" s="41" t="n"/>
+      <c r="G20" s="35" t="n"/>
+      <c r="H20" s="35" t="n"/>
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" s="36" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>20E / G.25</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Gate stopped</t>
         </is>
       </c>
-      <c r="C21" s="42" t="n"/>
-      <c r="D21" s="46" t="n">
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="40" t="n">
         <v>46300</v>
       </c>
-      <c r="E21" s="46" t="n">
+      <c r="E21" s="40" t="n">
         <v>46313</v>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>G.25 stops working 5–18 Oct 2026 to change trolley rail (in progress)  —  Unchanged</t>
         </is>
       </c>
-      <c r="G21" s="40" t="n"/>
-      <c r="H21" s="40" t="n"/>
-      <c r="I21" s="40" t="n"/>
-      <c r="J21" s="41" t="n"/>
+      <c r="G21" s="35" t="n"/>
+      <c r="H21" s="35" t="n"/>
+      <c r="I21" s="35" t="n"/>
+      <c r="J21" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/12-10-2026/PAT_Berth_Window.xlsx
+++ b/12-10-2026/PAT_Berth_Window.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="166" formatCode="[$-409]dd-mmm-yyyy hh:mm"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +65,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
@@ -171,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -230,7 +235,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -248,29 +253,30 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -730,13 +736,13 @@
       <c r="C4" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D4" s="39" t="n">
+      <c r="D4" s="40" t="n">
         <v>46307.33333333334</v>
       </c>
-      <c r="E4" s="39" t="n">
+      <c r="E4" s="40" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F4" s="39" t="n">
+      <c r="F4" s="40" t="n">
         <v>46309.20833333334</v>
       </c>
       <c r="G4" s="24">
@@ -768,13 +774,13 @@
       <c r="C5" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D5" s="39" t="n">
+      <c r="D5" s="40" t="n">
         <v>46308.04166666666</v>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E5" s="40" t="n">
         <v>46309.20833333334</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="40" t="n">
         <v>46310.625</v>
       </c>
       <c r="G5" s="24">
@@ -806,13 +812,13 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="40" t="n">
         <v>46307.91666666666</v>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="40" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="40" t="n">
         <v>46309.66666666666</v>
       </c>
       <c r="G6" s="24">
@@ -844,13 +850,13 @@
       <c r="C7" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="40" t="n">
         <v>46309.33333333334</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="40" t="n">
         <v>46309.66666666666</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="40" t="n">
         <v>46310.29166666666</v>
       </c>
       <c r="G7" s="24">
@@ -882,13 +888,13 @@
       <c r="C8" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="40" t="n">
         <v>46307.875</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="40" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="40" t="n">
         <v>46309.625</v>
       </c>
       <c r="G8" s="24">
@@ -920,13 +926,13 @@
       <c r="C9" s="23" t="n">
         <v>449</v>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="40" t="n">
         <v>46309.125</v>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="40" t="n">
         <v>46309.58333333334</v>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F9" s="40" t="n">
         <v>46310.20833333334</v>
       </c>
       <c r="G9" s="24">
@@ -958,13 +964,13 @@
       <c r="C10" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D10" s="40" t="n">
         <v>46305.70833333334</v>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E10" s="40" t="n">
         <v>46306.25</v>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="40" t="n">
         <v>46307.58333333334</v>
       </c>
       <c r="G10" s="24">
@@ -996,13 +1002,13 @@
       <c r="C11" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="40" t="n">
         <v>46307.16666666666</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="40" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="40" t="n">
         <v>46309.20833333334</v>
       </c>
       <c r="G11" s="24">
@@ -1034,13 +1040,13 @@
       <c r="C12" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="40" t="n">
         <v>46308.29166666666</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="40" t="n">
         <v>46309.20833333334</v>
       </c>
-      <c r="F12" s="39" t="n">
+      <c r="F12" s="40" t="n">
         <v>46309.91666666666</v>
       </c>
       <c r="G12" s="24">
@@ -1072,13 +1078,13 @@
       <c r="C13" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D13" s="40" t="n">
         <v>46307.45833333334</v>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="40" t="n">
         <v>46307.625</v>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F13" s="40" t="n">
         <v>46308.25</v>
       </c>
       <c r="G13" s="24">
@@ -1110,13 +1116,13 @@
       <c r="C14" s="23" t="n">
         <v>537</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="40" t="n">
         <v>46307.91666666666</v>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E14" s="40" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F14" s="39" t="n">
+      <c r="F14" s="40" t="n">
         <v>46309.25</v>
       </c>
       <c r="G14" s="24">
@@ -1148,13 +1154,13 @@
       <c r="C15" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D15" s="39" t="n">
+      <c r="D15" s="40" t="n">
         <v>46308.625</v>
       </c>
-      <c r="E15" s="39" t="n">
+      <c r="E15" s="40" t="n">
         <v>46309.25</v>
       </c>
-      <c r="F15" s="39" t="n">
+      <c r="F15" s="40" t="n">
         <v>46310.625</v>
       </c>
       <c r="G15" s="24">
@@ -1223,10 +1229,10 @@
         </is>
       </c>
       <c r="C20" s="38" t="n"/>
-      <c r="D20" s="40" t="n">
+      <c r="D20" s="41" t="n">
         <v>46299</v>
       </c>
-      <c r="E20" s="40" t="n">
+      <c r="E20" s="41" t="n">
         <v>46319</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
@@ -1251,10 +1257,10 @@
         </is>
       </c>
       <c r="C21" s="38" t="n"/>
-      <c r="D21" s="40" t="n">
+      <c r="D21" s="41" t="n">
         <v>46300</v>
       </c>
-      <c r="E21" s="40" t="n">
+      <c r="E21" s="41" t="n">
         <v>46313</v>
       </c>
       <c r="F21" s="16" t="inlineStr">

--- a/12-10-2026/PAT_Berth_Window.xlsx
+++ b/12-10-2026/PAT_Berth_Window.xlsx
@@ -244,6 +244,12 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -264,12 +270,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>

--- a/12-10-2026/PAT_Berth_Window.xlsx
+++ b/12-10-2026/PAT_Berth_Window.xlsx
@@ -176,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,6 +270,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -736,13 +745,13 @@
       <c r="C4" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D4" s="43" t="n">
         <v>46307.33333333334</v>
       </c>
-      <c r="E4" s="40" t="n">
+      <c r="E4" s="43" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F4" s="40" t="n">
+      <c r="F4" s="43" t="n">
         <v>46309.20833333334</v>
       </c>
       <c r="G4" s="24">
@@ -774,13 +783,13 @@
       <c r="C5" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D5" s="40" t="n">
+      <c r="D5" s="43" t="n">
         <v>46308.04166666666</v>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="43" t="n">
         <v>46309.20833333334</v>
       </c>
-      <c r="F5" s="40" t="n">
+      <c r="F5" s="43" t="n">
         <v>46310.625</v>
       </c>
       <c r="G5" s="24">
@@ -812,13 +821,13 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="43" t="n">
         <v>46307.91666666666</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="43" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="43" t="n">
         <v>46309.66666666666</v>
       </c>
       <c r="G6" s="24">
@@ -850,13 +859,13 @@
       <c r="C7" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="43" t="n">
         <v>46309.33333333334</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="43" t="n">
         <v>46309.66666666666</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="43" t="n">
         <v>46310.29166666666</v>
       </c>
       <c r="G7" s="24">
@@ -888,13 +897,13 @@
       <c r="C8" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="43" t="n">
         <v>46307.875</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="43" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="43" t="n">
         <v>46309.625</v>
       </c>
       <c r="G8" s="24">
@@ -926,13 +935,13 @@
       <c r="C9" s="23" t="n">
         <v>449</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="43" t="n">
         <v>46309.125</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="43" t="n">
         <v>46309.58333333334</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="43" t="n">
         <v>46310.20833333334</v>
       </c>
       <c r="G9" s="24">
@@ -964,13 +973,13 @@
       <c r="C10" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="43" t="n">
         <v>46305.70833333334</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="43" t="n">
         <v>46306.25</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="43" t="n">
         <v>46307.58333333334</v>
       </c>
       <c r="G10" s="24">
@@ -1002,13 +1011,13 @@
       <c r="C11" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="43" t="n">
         <v>46307.16666666666</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="43" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="43" t="n">
         <v>46309.20833333334</v>
       </c>
       <c r="G11" s="24">
@@ -1040,13 +1049,13 @@
       <c r="C12" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="43" t="n">
         <v>46308.29166666666</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="43" t="n">
         <v>46309.20833333334</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="43" t="n">
         <v>46309.91666666666</v>
       </c>
       <c r="G12" s="24">
@@ -1078,13 +1087,13 @@
       <c r="C13" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="43" t="n">
         <v>46307.45833333334</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="43" t="n">
         <v>46307.625</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="43" t="n">
         <v>46308.25</v>
       </c>
       <c r="G13" s="24">
@@ -1116,13 +1125,13 @@
       <c r="C14" s="23" t="n">
         <v>537</v>
       </c>
-      <c r="D14" s="40" t="n">
+      <c r="D14" s="43" t="n">
         <v>46307.91666666666</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E14" s="43" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="43" t="n">
         <v>46309.25</v>
       </c>
       <c r="G14" s="24">
@@ -1154,13 +1163,13 @@
       <c r="C15" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="43" t="n">
         <v>46308.625</v>
       </c>
-      <c r="E15" s="40" t="n">
+      <c r="E15" s="43" t="n">
         <v>46309.25</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="43" t="n">
         <v>46310.625</v>
       </c>
       <c r="G15" s="24">
@@ -1179,7 +1188,7 @@
       <c r="J15" s="23" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1212,10 +1221,10 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
-      <c r="I19" s="35" t="n"/>
-      <c r="J19" s="36" t="n"/>
+      <c r="G19" s="38" t="n"/>
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="39" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -1228,11 +1237,11 @@
           <t>Berth closed</t>
         </is>
       </c>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="41" t="n">
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="44" t="n">
         <v>46299</v>
       </c>
-      <c r="E20" s="41" t="n">
+      <c r="E20" s="44" t="n">
         <v>46319</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
@@ -1240,10 +1249,10 @@
           <t>Close on 4–24 Oct 2026 to renovate electric channel (INCEDA is alongside at 20D; other vessels are booked from 12/16)  —  Unchanged – conflicts with vessel bookings, please confirm</t>
         </is>
       </c>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
-      <c r="I20" s="35" t="n"/>
-      <c r="J20" s="36" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="38" t="n"/>
+      <c r="I20" s="38" t="n"/>
+      <c r="J20" s="39" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
@@ -1256,11 +1265,11 @@
           <t>Gate stopped</t>
         </is>
       </c>
-      <c r="C21" s="38" t="n"/>
-      <c r="D21" s="41" t="n">
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="44" t="n">
         <v>46300</v>
       </c>
-      <c r="E21" s="41" t="n">
+      <c r="E21" s="44" t="n">
         <v>46313</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
@@ -1268,10 +1277,10 @@
           <t>G.25 stops working 5–18 Oct 2026 to change trolley rail (in progress)  —  Unchanged</t>
         </is>
       </c>
-      <c r="G21" s="35" t="n"/>
-      <c r="H21" s="35" t="n"/>
-      <c r="I21" s="35" t="n"/>
-      <c r="J21" s="36" t="n"/>
+      <c r="G21" s="38" t="n"/>
+      <c r="H21" s="38" t="n"/>
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
